--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_valparaiso.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:41</t>
+    <t xml:space="preserve">2026-09-09 20:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_valparaiso.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Provincial" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Provincial_sexo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tramo_etario" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tramo_etario_nacional" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Media_nacional" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Provincial_sexo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tramo_etario" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tramo_etario_nacional" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Tramo_etario_nacional'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tramo_etario_nacional'!$A$1:$C$8</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -75,7 +76,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:45</t>
+    <t xml:space="preserve">2026-09-18 10:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -102,6 +103,9 @@
     <t xml:space="preserve">Año</t>
   </si>
   <si>
+    <t xml:space="preserve">Media nacional (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mujeres (%)</t>
   </si>
   <si>
@@ -133,9 +137,6 @@
   </si>
   <si>
     <t xml:space="preserve">16 a 17 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media nacional (%)</t>
   </si>
 </sst>
 </file>
@@ -952,6 +953,62 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>58.44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>94.28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>86.91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>43.38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="12.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="13.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
@@ -965,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -1426,7 +1483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -1445,136 +1502,136 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>24.76</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>53.31</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>83.52</v>
+        <v>88.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>23.45</v>
+        <v>24.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>55.65</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>94.21</v>
+        <v>83.52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>21.36</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>54.91</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>92.33</v>
+        <v>94.21</v>
       </c>
     </row>
     <row r="11">
@@ -1585,7 +1642,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>26.78</v>
@@ -1599,7 +1656,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>54.68</v>
@@ -1613,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>94.63</v>
@@ -1627,7 +1684,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>27.16</v>
@@ -1641,7 +1698,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>59.97</v>
@@ -1655,7 +1712,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>93.92</v>
@@ -1669,7 +1726,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>23.29</v>
@@ -1683,7 +1740,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>49.59</v>
@@ -1697,7 +1754,7 @@
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>90.21</v>
@@ -1711,7 +1768,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>30.62</v>
@@ -1725,7 +1782,7 @@
         <v>3</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>59.73</v>
@@ -1739,7 +1796,7 @@
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>94.64</v>
@@ -1747,128 +1804,128 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>19.53</v>
+        <v>21.36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>48.93</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>88.98</v>
+        <v>92.33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>92.2</v>
+        <v>93.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>94.94</v>
+        <v>93.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>94.55</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>96.23</v>
+        <v>94.94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>93.07</v>
+        <v>94.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>94.18</v>
+        <v>96.23</v>
       </c>
     </row>
     <row r="32">
@@ -1879,7 +1936,7 @@
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>94.94</v>
@@ -1893,7 +1950,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>95.75</v>
@@ -1907,7 +1964,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>93.97</v>
@@ -1921,7 +1978,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>95.39</v>
@@ -1935,7 +1992,7 @@
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>92.19</v>
@@ -1949,7 +2006,7 @@
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>92.68</v>
@@ -1963,7 +2020,7 @@
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>94.81</v>
@@ -1977,7 +2034,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>96.66</v>
@@ -1985,114 +2042,114 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>93.34</v>
+        <v>93.07</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>93.74</v>
+        <v>94.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>85.09</v>
+        <v>83.43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>84.66</v>
+        <v>86.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>88.95</v>
+        <v>85.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>87.77</v>
+        <v>84.66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>86.16</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>86.16</v>
+        <v>87.77</v>
       </c>
     </row>
     <row r="48">
@@ -2103,7 +2160,7 @@
         <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>91.05</v>
@@ -2117,7 +2174,7 @@
         <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>89.39</v>
@@ -2131,7 +2188,7 @@
         <v>13</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>86.11</v>
@@ -2145,7 +2202,7 @@
         <v>13</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>86.13</v>
@@ -2159,7 +2216,7 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>85.14</v>
@@ -2173,7 +2230,7 @@
         <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>86.12</v>
@@ -2187,7 +2244,7 @@
         <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>86.32</v>
@@ -2201,7 +2258,7 @@
         <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>87.24</v>
@@ -2209,30 +2266,30 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>83.43</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>86.09</v>
+        <v>86.16</v>
       </c>
     </row>
   </sheetData>
@@ -2242,7 +2299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
@@ -2257,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
@@ -2268,7 +2325,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>91.65</v>
@@ -2279,7 +2336,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>53.07</v>
@@ -2290,7 +2347,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>22.46</v>
@@ -2301,7 +2358,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>93.67</v>
@@ -2312,7 +2369,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>94.91</v>
@@ -2323,7 +2380,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>87.26</v>
@@ -2334,7 +2391,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>86.58</v>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_valparaiso.xlsx
@@ -76,7 +76,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:36</t>
+    <t xml:space="preserve">2026-09-23 16:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2022_valparaiso.xlsx
@@ -76,7 +76,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:20</t>
+    <t xml:space="preserve">2026-10-05 05:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
